--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-12T23:50:21+00:00</t>
+          <t>2026-09-13T15:29:47+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-12T23:50:21+00:00</t>
+          <t>2026-09-13T15:29:47+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-12T23:50:21+00:00</t>
+          <t>2026-09-13T15:29:47+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-12T23:50:21+00:00</t>
+          <t>2026-09-13T15:29:47+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-12T23:50:21+00:00</t>
+          <t>2026-09-13T15:29:47+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-12T23:50:21+00:00</t>
+          <t>2026-09-13T15:29:47+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-13T15:29:47+00:00</t>
+          <t>2026-09-13T18:37:24+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-13T15:29:47+00:00</t>
+          <t>2026-09-13T18:37:24+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-13T15:29:47+00:00</t>
+          <t>2026-09-13T18:37:24+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-13T15:29:47+00:00</t>
+          <t>2026-09-13T18:37:24+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-13T15:29:47+00:00</t>
+          <t>2026-09-13T18:37:24+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-13T15:29:47+00:00</t>
+          <t>2026-09-13T18:37:24+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-13T18:37:24+00:00</t>
+          <t>2026-09-13T23:56:25+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-13T18:37:24+00:00</t>
+          <t>2026-09-13T23:56:25+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-13T18:37:24+00:00</t>
+          <t>2026-09-13T23:56:25+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-13T18:37:24+00:00</t>
+          <t>2026-09-13T23:56:25+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-13T18:37:24+00:00</t>
+          <t>2026-09-13T23:56:25+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-13T18:37:24+00:00</t>
+          <t>2026-09-13T23:56:25+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-13T23:56:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-13T23:56:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-13T23:56:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-13T23:56:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-13T23:56:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-13T23:56:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-13T23:56:25+00:00</t>
+          <t>2026-09-14T17:28:40+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-13T23:56:25+00:00</t>
+          <t>2026-09-14T17:28:40+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-13T23:56:25+00:00</t>
+          <t>2026-09-14T17:28:40+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-13T23:56:25+00:00</t>
+          <t>2026-09-14T17:28:40+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-13T23:56:25+00:00</t>
+          <t>2026-09-14T17:28:40+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-13T23:56:25+00:00</t>
+          <t>2026-09-14T17:28:40+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-13T23:56:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-13T23:56:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-13T23:56:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-13T23:56:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-13T23:56:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-13T23:56:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:28:40+00:00</t>
+          <t>2026-09-14T20:12:35+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:28:40+00:00</t>
+          <t>2026-09-14T20:12:35+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-14T17:28:40+00:00</t>
+          <t>2026-09-14T20:12:35+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-14T17:28:40+00:00</t>
+          <t>2026-09-14T20:12:35+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-14T17:28:40+00:00</t>
+          <t>2026-09-14T20:12:35+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-14T17:28:40+00:00</t>
+          <t>2026-09-14T20:12:35+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,732 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-14T20:12:35+00:00</t>
+          <t>2026-09-15T00:23:04+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-14T20:12:35+00:00</t>
+          <t>2026-09-15T00:23:04+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-14T20:12:35+00:00</t>
+          <t>2026-09-15T00:23:04+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-14T20:12:35+00:00</t>
+          <t>2026-09-15T00:23:04+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-14T20:12:35+00:00</t>
+          <t>2026-09-15T00:23:04+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-14T20:12:35+00:00</t>
+          <t>2026-09-15T00:23:04+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,732 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-09-14T20:12:35+00:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-15T00:23:04+00:00</t>
+          <t>2026-09-15T16:05:24+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-15T00:23:04+00:00</t>
+          <t>2026-09-15T16:05:24+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-15T00:23:04+00:00</t>
+          <t>2026-09-15T16:05:24+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-15T00:23:04+00:00</t>
+          <t>2026-09-15T16:05:24+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-15T00:23:04+00:00</t>
+          <t>2026-09-15T16:05:24+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-15T00:23:04+00:00</t>
+          <t>2026-09-15T16:05:24+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-15T16:05:24+00:00</t>
+          <t>2026-09-15T19:35:04+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-15T19:35:04+00:00</t>
+          <t>2026-09-16T00:02:09+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1326,6 +1326,369 @@
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-09-16T00:02:09+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-16T00:02:09+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-09-16T00:02:09+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-16T00:02:09+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-09-16T00:02:09+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-16T00:02:09+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:27:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-16T19:27:01+00:00</t>
+          <t>2026-09-17T00:11:30+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-16T19:27:01+00:00</t>
+          <t>2026-09-17T00:11:30+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-16T19:27:01+00:00</t>
+          <t>2026-09-17T00:11:30+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-16T19:27:01+00:00</t>
+          <t>2026-09-17T00:11:30+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-16T19:27:01+00:00</t>
+          <t>2026-09-17T00:11:30+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-16T19:27:01+00:00</t>
+          <t>2026-09-17T00:11:30+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-16T19:27:01+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-16T19:27:01+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-16T19:27:01+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-16T19:27:01+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-16T19:27:01+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-16T19:27:01+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:11:30+00:00</t>
+          <t>2026-09-17T16:04:50+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:11:30+00:00</t>
+          <t>2026-09-17T16:04:50+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-17T00:11:30+00:00</t>
+          <t>2026-09-17T16:04:50+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-17T00:11:30+00:00</t>
+          <t>2026-09-17T16:04:50+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-17T00:11:30+00:00</t>
+          <t>2026-09-17T16:04:50+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-17T00:11:30+00:00</t>
+          <t>2026-09-17T16:04:50+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:04:50+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:04:50+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:04:50+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:04:50+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:04:50+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:04:50+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-17T16:04:50+00:00</t>
+          <t>2026-09-17T19:37:18+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-17T16:04:50+00:00</t>
+          <t>2026-09-17T19:37:18+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-17T16:04:50+00:00</t>
+          <t>2026-09-17T19:37:18+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-17T16:04:50+00:00</t>
+          <t>2026-09-17T19:37:18+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-17T16:04:50+00:00</t>
+          <t>2026-09-17T19:37:18+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-17T16:04:50+00:00</t>
+          <t>2026-09-17T19:37:18+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-17T16:04:50+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-17T16:04:50+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-17T16:04:50+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-17T16:04:50+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-17T16:04:50+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-17T16:04:50+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-17T19:37:18+00:00</t>
+          <t>2026-09-17T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-17T19:37:18+00:00</t>
+          <t>2026-09-17T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-17T19:37:18+00:00</t>
+          <t>2026-09-17T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-17T19:37:18+00:00</t>
+          <t>2026-09-17T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-17T19:37:18+00:00</t>
+          <t>2026-09-17T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-17T19:37:18+00:00</t>
+          <t>2026-09-17T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-17T23:58:16+00:00</t>
+          <t>2026-09-18T15:41:02+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-17T23:58:16+00:00</t>
+          <t>2026-09-18T15:41:02+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-17T23:58:16+00:00</t>
+          <t>2026-09-18T15:41:02+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-17T23:58:16+00:00</t>
+          <t>2026-09-18T15:41:02+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-17T23:58:16+00:00</t>
+          <t>2026-09-18T15:41:02+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-17T23:58:16+00:00</t>
+          <t>2026-09-18T15:41:02+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:02+00:00</t>
+          <t>2026-09-18T18:56:54+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:02+00:00</t>
+          <t>2026-09-18T18:56:54+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:02+00:00</t>
+          <t>2026-09-18T18:56:54+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:02+00:00</t>
+          <t>2026-09-18T18:56:54+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:02+00:00</t>
+          <t>2026-09-18T18:56:54+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:02+00:00</t>
+          <t>2026-09-18T18:56:54+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-18T18:56:54+00:00</t>
+          <t>2026-09-18T23:57:00+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-18T18:56:54+00:00</t>
+          <t>2026-09-18T23:57:00+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-18T18:56:54+00:00</t>
+          <t>2026-09-18T23:57:00+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-18T18:56:54+00:00</t>
+          <t>2026-09-18T23:57:00+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-18T18:56:54+00:00</t>
+          <t>2026-09-18T23:57:00+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-18T18:56:54+00:00</t>
+          <t>2026-09-18T23:57:00+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-18T23:57:00+00:00</t>
+          <t>2026-09-19T15:13:05+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-18T23:57:00+00:00</t>
+          <t>2026-09-19T15:13:05+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-18T23:57:00+00:00</t>
+          <t>2026-09-19T15:13:05+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-18T23:57:00+00:00</t>
+          <t>2026-09-19T15:13:05+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-18T23:57:00+00:00</t>
+          <t>2026-09-19T15:13:05+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-18T23:57:00+00:00</t>
+          <t>2026-09-19T15:13:05+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-18T23:57:00+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-18T23:57:00+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-18T23:57:00+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-18T23:57:00+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-18T23:57:00+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-18T23:57:00+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-19T15:13:05+00:00</t>
+          <t>2026-09-19T18:29:42+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-19T15:13:05+00:00</t>
+          <t>2026-09-19T18:29:42+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-19T15:13:05+00:00</t>
+          <t>2026-09-19T18:29:42+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-19T15:13:05+00:00</t>
+          <t>2026-09-19T18:29:42+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-19T15:13:05+00:00</t>
+          <t>2026-09-19T18:29:42+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-19T15:13:05+00:00</t>
+          <t>2026-09-19T18:29:42+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-19T18:29:42+00:00</t>
+          <t>2026-09-19T23:57:22+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-19T18:29:42+00:00</t>
+          <t>2026-09-19T23:57:22+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-19T18:29:42+00:00</t>
+          <t>2026-09-19T23:57:22+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-19T18:29:42+00:00</t>
+          <t>2026-09-19T23:57:22+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-19T18:29:42+00:00</t>
+          <t>2026-09-19T23:57:22+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-19T18:29:42+00:00</t>
+          <t>2026-09-19T23:57:22+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:57:22+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:57:22+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:57:22+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:57:22+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:57:22+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:57:22+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:34:48+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:34:48+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:34:48+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:34:48+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:34:48+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:34:48+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-20T18:34:48+00:00</t>
+          <t>2026-09-20T23:55:38+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-20T18:34:48+00:00</t>
+          <t>2026-09-20T23:55:38+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-20T18:34:48+00:00</t>
+          <t>2026-09-20T23:55:38+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-20T18:34:48+00:00</t>
+          <t>2026-09-20T23:55:38+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-20T18:34:48+00:00</t>
+          <t>2026-09-20T23:55:38+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-20T18:34:48+00:00</t>
+          <t>2026-09-20T23:55:38+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-20T23:55:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-20T23:55:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-20T23:55:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-20T23:55:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-20T23:55:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-20T23:55:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-20T23:55:38+00:00</t>
+          <t>2026-09-21T17:42:41+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-21T17:42:41+00:00</t>
+          <t>2026-09-21T20:19:13+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-21T17:42:41+00:00</t>
+          <t>2026-09-21T20:19:13+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-21T17:42:41+00:00</t>
+          <t>2026-09-21T20:19:13+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-21T17:42:41+00:00</t>
+          <t>2026-09-21T20:19:13+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-21T17:42:41+00:00</t>
+          <t>2026-09-21T20:19:13+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-21T17:42:41+00:00</t>
+          <t>2026-09-21T20:19:13+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-21T17:42:41+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-21T17:42:41+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-21T17:42:41+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-21T17:42:41+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-21T17:42:41+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-21T17:42:41+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-21T20:19:13+00:00</t>
+          <t>2026-09-22T00:38:49+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-21T20:19:13+00:00</t>
+          <t>2026-09-22T00:38:49+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-21T20:19:13+00:00</t>
+          <t>2026-09-22T00:38:49+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-21T20:19:13+00:00</t>
+          <t>2026-09-22T00:38:49+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-21T20:19:13+00:00</t>
+          <t>2026-09-22T00:38:49+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-21T20:19:13+00:00</t>
+          <t>2026-09-22T00:38:49+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:38:49+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:38:49+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:38:49+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:38:49+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:38:49+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:38:49+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-22T00:38:49+00:00</t>
+          <t>2026-09-22T16:08:03+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-22T00:38:49+00:00</t>
+          <t>2026-09-22T16:08:03+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-22T00:38:49+00:00</t>
+          <t>2026-09-22T16:08:03+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22T00:38:49+00:00</t>
+          <t>2026-09-22T16:08:03+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-22T00:38:49+00:00</t>
+          <t>2026-09-22T16:08:03+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22T00:38:49+00:00</t>
+          <t>2026-09-22T16:08:03+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-22T00:38:49+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-22T00:38:49+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-22T00:38:49+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-22T00:38:49+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-22T00:38:49+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-22T00:38:49+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-09-22T16:08:03+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-09-22T16:08:03+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-09-22T16:08:03+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-09-22T16:08:03+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-09-22T16:08:03+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-09-22T16:08:03+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-23T00:06:11+00:00</t>
+          <t>2026-09-23T15:58:16+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-23T00:06:11+00:00</t>
+          <t>2026-09-23T15:58:16+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-23T00:06:11+00:00</t>
+          <t>2026-09-23T15:58:16+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-23T00:06:11+00:00</t>
+          <t>2026-09-23T15:58:16+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-23T00:06:11+00:00</t>
+          <t>2026-09-23T15:58:16+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-23T00:06:11+00:00</t>
+          <t>2026-09-23T15:58:16+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-23T00:06:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-23T00:06:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-23T00:06:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-23T00:06:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-23T00:06:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-23T00:06:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:58:16+00:00</t>
+          <t>2026-09-23T19:33:52+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:58:16+00:00</t>
+          <t>2026-09-23T19:33:52+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-23T15:58:16+00:00</t>
+          <t>2026-09-23T19:33:52+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-23T15:58:16+00:00</t>
+          <t>2026-09-23T19:33:52+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-23T15:58:16+00:00</t>
+          <t>2026-09-23T19:33:52+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-23T15:58:16+00:00</t>
+          <t>2026-09-23T19:33:52+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:33:52+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:33:52+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:33:52+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:33:52+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:33:52+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:33:52+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-23T19:33:52+00:00</t>
+          <t>2026-09-24T00:17:27+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-23T19:33:52+00:00</t>
+          <t>2026-09-24T00:17:27+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-23T19:33:52+00:00</t>
+          <t>2026-09-24T00:17:27+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-23T19:33:52+00:00</t>
+          <t>2026-09-24T00:17:27+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-23T19:33:52+00:00</t>
+          <t>2026-09-24T00:17:27+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-23T19:33:52+00:00</t>
+          <t>2026-09-24T00:17:27+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-23T19:33:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-23T19:33:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-23T19:33:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-23T19:33:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-23T19:33:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-23T19:33:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-09-24T00:17:27+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-09-24T00:17:27+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-09-24T00:17:27+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-09-24T00:17:27+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-09-24T00:17:27+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-09-24T00:17:27+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,1206 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:21:41+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:21:41+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:21:41+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:21:41+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:21:41+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-25T16:21:41+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:21:41+00:00</t>
+          <t>2026-09-25T19:55:27+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:21:41+00:00</t>
+          <t>2026-09-25T19:55:27+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-25T16:21:41+00:00</t>
+          <t>2026-09-25T19:55:27+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-25T16:21:41+00:00</t>
+          <t>2026-09-25T19:55:27+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-25T16:21:41+00:00</t>
+          <t>2026-09-25T19:55:27+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-25T16:21:41+00:00</t>
+          <t>2026-09-25T19:55:27+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,732 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1334,7 +1334,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1455,7 +1455,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -1576,7 +1576,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-25T19:55:27+00:00</t>
+          <t>2026-09-26T00:25:39+00:00</t>
         </is>
       </c>
       <c r="AB10" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-26T00:25:39+00:00</t>
+          <t>2026-09-26T15:35:49+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-26T00:25:39+00:00</t>
+          <t>2026-09-26T15:35:49+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-26T00:25:39+00:00</t>
+          <t>2026-09-26T15:35:49+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-26T00:25:39+00:00</t>
+          <t>2026-09-26T15:35:49+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-26T00:25:39+00:00</t>
+          <t>2026-09-26T15:35:49+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-26T00:25:39+00:00</t>
+          <t>2026-09-26T15:35:49+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,732 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-09-26T00:25:39+00:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-26T15:35:49+00:00</t>
+          <t>2026-09-26T19:06:40+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-26T15:35:49+00:00</t>
+          <t>2026-09-26T19:06:40+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-26T15:35:49+00:00</t>
+          <t>2026-09-26T19:06:40+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-26T15:35:49+00:00</t>
+          <t>2026-09-26T19:06:40+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-26T15:35:49+00:00</t>
+          <t>2026-09-26T19:06:40+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-26T15:35:49+00:00</t>
+          <t>2026-09-26T19:06:40+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-26T19:06:40+00:00</t>
+          <t>2026-09-27T00:20:15+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-26T19:06:40+00:00</t>
+          <t>2026-09-27T00:20:15+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-26T19:06:40+00:00</t>
+          <t>2026-09-27T00:20:15+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-26T19:06:40+00:00</t>
+          <t>2026-09-27T00:20:15+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-26T19:06:40+00:00</t>
+          <t>2026-09-27T00:20:15+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-26T19:06:40+00:00</t>
+          <t>2026-09-27T00:20:15+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-27T00:20:15+00:00</t>
+          <t>2026-09-27T16:15:11+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-27T00:20:15+00:00</t>
+          <t>2026-09-27T16:15:11+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-27T00:20:15+00:00</t>
+          <t>2026-09-27T16:15:11+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-27T00:20:15+00:00</t>
+          <t>2026-09-27T16:15:11+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-27T00:20:15+00:00</t>
+          <t>2026-09-27T16:15:11+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-27T00:20:15+00:00</t>
+          <t>2026-09-27T16:15:11+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-27T16:15:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-27T16:15:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-27T16:15:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-27T16:15:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-27T16:15:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-27T16:15:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-27T16:15:11+00:00</t>
+          <t>2026-09-27T19:38:48+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-27T16:15:11+00:00</t>
+          <t>2026-09-27T19:38:48+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-27T16:15:11+00:00</t>
+          <t>2026-09-27T19:38:48+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-27T16:15:11+00:00</t>
+          <t>2026-09-27T19:38:48+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-27T16:15:11+00:00</t>
+          <t>2026-09-27T19:38:48+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-27T16:15:11+00:00</t>
+          <t>2026-09-27T19:38:48+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-27T16:15:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-27T16:15:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-27T16:15:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-27T16:15:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-27T16:15:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-27T16:15:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-27T19:38:48+00:00</t>
+          <t>2026-09-28T00:22:19+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-27T19:38:48+00:00</t>
+          <t>2026-09-28T00:22:19+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-27T19:38:48+00:00</t>
+          <t>2026-09-28T00:22:19+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-27T19:38:48+00:00</t>
+          <t>2026-09-28T00:22:19+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-27T19:38:48+00:00</t>
+          <t>2026-09-28T00:22:19+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-27T19:38:48+00:00</t>
+          <t>2026-09-28T00:22:19+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-28T00:22:19+00:00</t>
+          <t>2026-09-28T19:08:14+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-28T00:22:19+00:00</t>
+          <t>2026-09-28T19:08:14+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-28T00:22:19+00:00</t>
+          <t>2026-09-28T19:08:14+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-28T00:22:19+00:00</t>
+          <t>2026-09-28T19:08:14+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-28T00:22:19+00:00</t>
+          <t>2026-09-28T19:08:14+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-28T00:22:19+00:00</t>
+          <t>2026-09-28T19:08:14+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-28T19:08:14+00:00</t>
+          <t>2026-09-28T21:40:58+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-28T19:08:14+00:00</t>
+          <t>2026-09-28T21:40:58+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-28T19:08:14+00:00</t>
+          <t>2026-09-28T21:40:58+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-28T19:08:14+00:00</t>
+          <t>2026-09-28T21:40:58+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-28T19:08:14+00:00</t>
+          <t>2026-09-28T21:40:58+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-28T19:08:14+00:00</t>
+          <t>2026-09-28T21:40:58+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-09-28T21:40:58+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-09-28T21:40:58+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-09-28T21:40:58+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-09-28T21:40:58+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-09-28T21:40:58+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-09-28T21:40:58+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-29T17:30:07+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-29T17:30:07+00:00</t>
+          <t>2026-09-29T20:32:11+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-29T20:32:11+00:00</t>
+          <t>2026-09-30T01:08:40+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-30T01:08:40+00:00</t>
+          <t>2026-09-30T17:28:10+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-30T01:08:40+00:00</t>
+          <t>2026-09-30T17:28:10+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-30T01:08:40+00:00</t>
+          <t>2026-09-30T17:28:10+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-30T01:08:40+00:00</t>
+          <t>2026-09-30T17:28:10+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-30T01:08:40+00:00</t>
+          <t>2026-09-30T17:28:10+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-30T01:08:40+00:00</t>
+          <t>2026-09-30T17:28:10+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-09-30T01:08:40+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-09-30T01:08:40+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-09-30T01:08:40+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-09-30T01:08:40+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-09-30T01:08:40+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-09-30T01:08:40+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-30T17:28:10+00:00</t>
+          <t>2026-09-30T20:39:23+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-30T17:28:10+00:00</t>
+          <t>2026-09-30T20:39:23+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-30T17:28:10+00:00</t>
+          <t>2026-09-30T20:39:23+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-30T17:28:10+00:00</t>
+          <t>2026-09-30T20:39:23+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-30T17:28:10+00:00</t>
+          <t>2026-09-30T20:39:23+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-30T17:28:10+00:00</t>
+          <t>2026-09-30T20:39:23+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-30T20:39:23+00:00</t>
+          <t>2026-10-01T01:08:25+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-30T20:39:23+00:00</t>
+          <t>2026-10-01T01:08:25+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-30T20:39:23+00:00</t>
+          <t>2026-10-01T01:08:25+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-30T20:39:23+00:00</t>
+          <t>2026-10-01T01:08:25+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-30T20:39:23+00:00</t>
+          <t>2026-10-01T01:08:25+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-30T20:39:23+00:00</t>
+          <t>2026-10-01T01:08:25+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,732 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-01T01:08:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-01T01:08:25+00:00</t>
+          <t>2026-10-01T17:54:52+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-01T01:08:25+00:00</t>
+          <t>2026-10-01T17:54:52+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-01T01:08:25+00:00</t>
+          <t>2026-10-01T17:54:52+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-01T01:08:25+00:00</t>
+          <t>2026-10-01T17:54:52+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-01T01:08:25+00:00</t>
+          <t>2026-10-01T17:54:52+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-01T01:08:25+00:00</t>
+          <t>2026-10-01T17:54:52+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,732 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-10-01T01:08:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-01T17:54:52+00:00</t>
+          <t>2026-10-01T20:53:31+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-01T17:54:52+00:00</t>
+          <t>2026-10-01T20:53:31+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-01T17:54:52+00:00</t>
+          <t>2026-10-01T20:53:31+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-01T17:54:52+00:00</t>
+          <t>2026-10-01T20:53:31+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-01T17:54:52+00:00</t>
+          <t>2026-10-01T20:53:31+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-01T17:54:52+00:00</t>
+          <t>2026-10-01T20:53:31+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,732 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:53:31+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-02T17:18:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-02T17:18:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-02T17:18:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-02T17:18:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-02T17:18:01+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-02T17:18:01+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-02T17:18:01+00:00</t>
+          <t>2026-10-02T20:28:46+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-02T17:18:01+00:00</t>
+          <t>2026-10-02T20:28:46+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-02T17:18:01+00:00</t>
+          <t>2026-10-02T20:28:46+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-02T17:18:01+00:00</t>
+          <t>2026-10-02T20:28:46+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-02T17:18:01+00:00</t>
+          <t>2026-10-02T20:28:46+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-02T17:18:01+00:00</t>
+          <t>2026-10-02T20:28:46+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-02T20:28:46+00:00</t>
+          <t>2026-10-03T00:59:26+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-02T20:28:46+00:00</t>
+          <t>2026-10-03T00:59:26+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-02T20:28:46+00:00</t>
+          <t>2026-10-03T00:59:26+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-02T20:28:46+00:00</t>
+          <t>2026-10-03T00:59:26+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-02T20:28:46+00:00</t>
+          <t>2026-10-03T00:59:26+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-02T20:28:46+00:00</t>
+          <t>2026-10-03T00:59:26+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-03T00:59:26+00:00</t>
+          <t>2026-10-03T15:36:13+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-03T00:59:26+00:00</t>
+          <t>2026-10-03T15:36:13+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-03T00:59:26+00:00</t>
+          <t>2026-10-03T15:36:13+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-03T00:59:26+00:00</t>
+          <t>2026-10-03T15:36:13+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-03T00:59:26+00:00</t>
+          <t>2026-10-03T15:36:13+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-03T00:59:26+00:00</t>
+          <t>2026-10-03T15:36:13+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-03T00:59:26+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-03T00:59:26+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-03T00:59:26+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-03T00:59:26+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-03T00:59:26+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-03T00:59:26+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-10-03T15:36:13+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-10-03T15:36:13+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-10-03T15:36:13+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-10-03T15:36:13+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-10-03T15:36:13+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-10-03T15:36:13+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-04T00:24:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-04T00:24:16+00:00</t>
+          <t>2026-10-04T16:20:14+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-04T16:20:14+00:00</t>
+          <t>2026-10-04T19:19:39+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1326,6 +1326,369 @@
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-05T22:22:57+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-05T22:22:57+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-05T22:22:57+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-05T22:22:57+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-05T22:22:57+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-05T22:22:57+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-10-05T22:22:57+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-10-05T22:22:57+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-10-05T22:22:57+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-10-05T22:22:57+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-10-05T22:22:57+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-10-05T22:22:57+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:47:43+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:47:43+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:47:43+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:47:43+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:47:43+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:47:43+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-06T17:47:43+00:00</t>
+          <t>2026-10-06T20:51:10+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-06T17:47:43+00:00</t>
+          <t>2026-10-06T20:51:10+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-06T17:47:43+00:00</t>
+          <t>2026-10-06T20:51:10+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-06T17:47:43+00:00</t>
+          <t>2026-10-06T20:51:10+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-06T17:47:43+00:00</t>
+          <t>2026-10-06T20:51:10+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-06T17:47:43+00:00</t>
+          <t>2026-10-06T20:51:10+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-06T20:51:10+00:00</t>
+          <t>2026-10-07T01:19:43+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-06T20:51:10+00:00</t>
+          <t>2026-10-07T01:19:43+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-06T20:51:10+00:00</t>
+          <t>2026-10-07T01:19:43+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-06T20:51:10+00:00</t>
+          <t>2026-10-07T01:19:43+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-06T20:51:10+00:00</t>
+          <t>2026-10-07T01:19:43+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-06T20:51:10+00:00</t>
+          <t>2026-10-07T01:19:43+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-07T01:19:43+00:00</t>
+          <t>2026-10-07T18:19:18+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-07T01:19:43+00:00</t>
+          <t>2026-10-07T18:19:18+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-07T01:19:43+00:00</t>
+          <t>2026-10-07T18:19:18+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-07T01:19:43+00:00</t>
+          <t>2026-10-07T18:19:18+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-07T01:19:43+00:00</t>
+          <t>2026-10-07T18:19:18+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-07T01:19:43+00:00</t>
+          <t>2026-10-07T18:19:18+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-07T18:19:18+00:00</t>
+          <t>2026-10-07T21:06:15+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-07T21:06:15+00:00</t>
+          <t>2026-10-08T01:37:02+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-07T21:06:15+00:00</t>
+          <t>2026-10-08T01:37:02+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-07T21:06:15+00:00</t>
+          <t>2026-10-08T01:37:02+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-07T21:06:15+00:00</t>
+          <t>2026-10-08T01:37:02+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-07T21:06:15+00:00</t>
+          <t>2026-10-08T01:37:02+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-07T21:06:15+00:00</t>
+          <t>2026-10-08T01:37:02+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-07T21:06:15+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-07T21:06:15+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-07T21:06:15+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-07T21:06:15+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-07T21:06:15+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-07T21:06:15+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:37:02+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:37:02+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:37:02+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:37:02+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:37:02+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-10-08T01:37:02+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:08:59+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-08T21:08:59+00:00</t>
+          <t>2026-10-09T01:47:52+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-09T01:47:52+00:00</t>
+          <t>2026-10-09T17:52:55+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-09T01:47:52+00:00</t>
+          <t>2026-10-09T17:52:55+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-09T01:47:52+00:00</t>
+          <t>2026-10-09T17:52:55+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-09T01:47:52+00:00</t>
+          <t>2026-10-09T17:52:55+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-09T01:47:52+00:00</t>
+          <t>2026-10-09T17:52:55+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-09T01:47:52+00:00</t>
+          <t>2026-10-09T17:52:55+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-09T01:47:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-09T01:47:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-09T01:47:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-09T01:47:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-09T01:47:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-09T01:47:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-09T17:52:55+00:00</t>
+          <t>2026-10-09T20:40:12+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-09T17:52:55+00:00</t>
+          <t>2026-10-09T20:40:12+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-09T17:52:55+00:00</t>
+          <t>2026-10-09T20:40:12+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-09T17:52:55+00:00</t>
+          <t>2026-10-09T20:40:12+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-09T17:52:55+00:00</t>
+          <t>2026-10-09T20:40:12+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-09T17:52:55+00:00</t>
+          <t>2026-10-09T20:40:12+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:40:12+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:40:12+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:40:12+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:40:12+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:40:12+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:40:12+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:49:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-10T16:49:46+00:00</t>
+          <t>2026-10-10T19:54:14+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1326,6 +1326,369 @@
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:54:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:54:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:54:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:54:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:54:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:54:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,1327 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-11T17:14:14+00:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-11T17:14:14+00:00</t>
+          <t>2026-10-11T20:01:20+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1326,490 +1326,6 @@
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:14:14+00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:14:14+00:00</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:14:14+00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:14:14+00:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:14:14+00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:14:14+00:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="b">
-        <v>0</v>
-      </c>
-      <c r="T11" t="b">
-        <v>0</v>
-      </c>
-      <c r="U11" t="b">
-        <v>0</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:14:14+00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-10-11T17:14:14+00:00</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-12T20:47:40+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-12T20:47:40+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-12T20:47:40+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-12T20:47:40+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-12T20:47:40+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-12T20:47:40+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-12T20:47:40+00:00</t>
+          <t>2026-10-12T22:48:13+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-12T20:47:40+00:00</t>
+          <t>2026-10-12T22:48:13+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-12T20:47:40+00:00</t>
+          <t>2026-10-12T22:48:13+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-12T20:47:40+00:00</t>
+          <t>2026-10-12T22:48:13+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:47:40+00:00</t>
+          <t>2026-10-12T22:48:13+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:47:40+00:00</t>
+          <t>2026-10-12T22:48:13+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-12T22:48:13+00:00</t>
+          <t>2026-10-13T02:53:32+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-12T22:48:13+00:00</t>
+          <t>2026-10-13T02:53:32+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-12T22:48:13+00:00</t>
+          <t>2026-10-13T02:53:32+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-12T22:48:13+00:00</t>
+          <t>2026-10-13T02:53:32+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-12T22:48:13+00:00</t>
+          <t>2026-10-13T02:53:32+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-12T22:48:13+00:00</t>
+          <t>2026-10-13T02:53:32+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:53:32+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:53:32+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:53:32+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:53:32+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:53:32+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:53:32+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-13T02:53:32+00:00</t>
+          <t>2026-10-13T18:47:11+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1326,6 +1326,369 @@
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-13T18:47:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-13T18:47:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-13T18:47:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-13T18:47:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-13T18:47:11+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-13T18:47:11+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-13T18:47:11+00:00</t>
+          <t>2026-10-13T21:03:19+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1326,369 +1326,6 @@
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2026-10-13T18:47:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-10-13T18:47:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2026-10-13T18:47:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-10-13T18:47:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2026-10-13T18:47:11+00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-10-13T18:47:11+00:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-13T21:03:19+00:00</t>
+          <t>2026-10-14T00:56:32+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-14T00:56:32+00:00</t>
+          <t>2026-10-14T16:22:07+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-14T00:56:32+00:00</t>
+          <t>2026-10-14T16:22:07+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-14T00:56:32+00:00</t>
+          <t>2026-10-14T16:22:07+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-14T00:56:32+00:00</t>
+          <t>2026-10-14T16:22:07+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-14T00:56:32+00:00</t>
+          <t>2026-10-14T16:22:07+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-14T00:56:32+00:00</t>
+          <t>2026-10-14T16:22:07+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-14T00:56:32+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-14T00:56:32+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-14T00:56:32+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-14T00:56:32+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-14T00:56:32+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-14T00:56:32+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-10-14T16:22:07+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-10-14T16:22:07+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-10-14T16:22:07+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-10-14T16:22:07+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-10-14T16:22:07+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-10-14T16:22:07+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-15T00:19:46+00:00</t>
+          <t>2026-10-15T16:10:11+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-15T16:10:11+00:00</t>
+          <t>2026-10-15T19:46:16+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-15T19:46:16+00:00</t>
+          <t>2026-10-16T00:07:49+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,1206 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-17T18:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-17T18:17:21+00:00</t>
+          <t>2026-10-17T23:49:52+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17T18:17:21+00:00</t>
+          <t>2026-10-17T23:49:52+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-17T18:17:21+00:00</t>
+          <t>2026-10-17T23:49:52+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-17T18:17:21+00:00</t>
+          <t>2026-10-17T23:49:52+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-17T18:17:21+00:00</t>
+          <t>2026-10-17T23:49:52+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-17T18:17:21+00:00</t>
+          <t>2026-10-17T23:49:52+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-17T18:17:21+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-17T18:17:21+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-17T18:17:21+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-17T18:17:21+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-17T18:17:21+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-17T18:17:21+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-10-17T23:49:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-10-17T23:49:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-10-17T23:49:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-10-17T23:49:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-10-17T23:49:52+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-10-17T23:49:52+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,843 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-18T18:31:24+00:00</t>
+          <t>2026-10-18T23:58:16+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1326,6 +1326,369 @@
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-18T23:58:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-18T23:58:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-18T23:58:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-18T23:58:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-18T23:58:16+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-18T23:58:16+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/annonces/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-18T23:58:16+00:00</t>
+          <t>2026-10-19T18:12:25+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1326,369 +1326,6 @@
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2026-10-18T23:58:16+00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-10-18T23:58:16+00:00</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2026-10-18T23:58:16+00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-10-18T23:58:16+00:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2026-10-18T23:58:16+00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-10-18T23:58:16+00:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-19T18:12:25+00:00</t>
+          <t>2026-10-19T20:55:53+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-19T18:12:25+00:00</t>
+          <t>2026-10-19T20:55:53+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-19T18:12:25+00:00</t>
+          <t>2026-10-19T20:55:53+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-19T18:12:25+00:00</t>
+          <t>2026-10-19T20:55:53+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-19T18:12:25+00:00</t>
+          <t>2026-10-19T20:55:53+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-19T18:12:25+00:00</t>
+          <t>2026-10-19T20:55:53+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-19T18:12:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-19T18:12:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-19T18:12:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-19T18:12:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-19T18:12:25+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-19T18:12:25+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-19T20:55:53+00:00</t>
+          <t>2026-10-20T00:56:34+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-19T20:55:53+00:00</t>
+          <t>2026-10-20T00:56:34+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-19T20:55:53+00:00</t>
+          <t>2026-10-20T00:56:34+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-19T20:55:53+00:00</t>
+          <t>2026-10-20T00:56:34+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-19T20:55:53+00:00</t>
+          <t>2026-10-20T00:56:34+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-19T20:55:53+00:00</t>
+          <t>2026-10-20T00:56:34+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-20T00:56:34+00:00</t>
+          <t>2026-10-20T16:13:28+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T00:56:34+00:00</t>
+          <t>2026-10-20T16:13:28+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-20T00:56:34+00:00</t>
+          <t>2026-10-20T16:13:28+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T00:56:34+00:00</t>
+          <t>2026-10-20T16:13:28+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-20T00:56:34+00:00</t>
+          <t>2026-10-20T16:13:28+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T00:56:34+00:00</t>
+          <t>2026-10-20T16:13:28+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-20T16:13:28+00:00</t>
+          <t>2026-10-20T19:54:43+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T16:13:28+00:00</t>
+          <t>2026-10-20T19:54:43+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-20T16:13:28+00:00</t>
+          <t>2026-10-20T19:54:43+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T16:13:28+00:00</t>
+          <t>2026-10-20T19:54:43+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-20T16:13:28+00:00</t>
+          <t>2026-10-20T19:54:43+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T16:13:28+00:00</t>
+          <t>2026-10-20T19:54:43+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-20T19:54:43+00:00</t>
+          <t>2026-10-21T00:24:54+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T19:54:43+00:00</t>
+          <t>2026-10-21T00:24:54+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-20T19:54:43+00:00</t>
+          <t>2026-10-21T00:24:54+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T19:54:43+00:00</t>
+          <t>2026-10-21T00:24:54+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-20T19:54:43+00:00</t>
+          <t>2026-10-21T00:24:54+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T19:54:43+00:00</t>
+          <t>2026-10-21T00:24:54+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-21T00:24:54+00:00</t>
+          <t>2026-10-21T16:28:51+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-21T00:24:54+00:00</t>
+          <t>2026-10-21T16:28:51+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-21T00:24:54+00:00</t>
+          <t>2026-10-21T16:28:51+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-21T00:24:54+00:00</t>
+          <t>2026-10-21T16:28:51+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-21T00:24:54+00:00</t>
+          <t>2026-10-21T16:28:51+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-21T00:24:54+00:00</t>
+          <t>2026-10-21T16:28:51+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:28:51+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:28:51+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:28:51+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:28:51+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:28:51+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:28:51+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-21T16:28:51+00:00</t>
+          <t>2026-10-21T19:58:49+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-21T16:28:51+00:00</t>
+          <t>2026-10-21T19:58:49+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-21T16:28:51+00:00</t>
+          <t>2026-10-21T19:58:49+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-21T16:28:51+00:00</t>
+          <t>2026-10-21T19:58:49+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-21T16:28:51+00:00</t>
+          <t>2026-10-21T19:58:49+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-21T16:28:51+00:00</t>
+          <t>2026-10-21T19:58:49+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:28:51+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:28:51+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:28:51+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:28:51+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:28:51+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:28:51+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-21T19:58:49+00:00</t>
+          <t>2026-10-22T00:28:45+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-21T19:58:49+00:00</t>
+          <t>2026-10-22T00:28:45+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-21T19:58:49+00:00</t>
+          <t>2026-10-22T00:28:45+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-21T19:58:49+00:00</t>
+          <t>2026-10-22T00:28:45+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-21T19:58:49+00:00</t>
+          <t>2026-10-22T00:28:45+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-21T19:58:49+00:00</t>
+          <t>2026-10-22T00:28:45+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-22T00:28:45+00:00</t>
+          <t>2026-10-22T16:29:12+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-22T00:28:45+00:00</t>
+          <t>2026-10-22T16:29:12+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-22T00:28:45+00:00</t>
+          <t>2026-10-22T16:29:12+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-22T00:28:45+00:00</t>
+          <t>2026-10-22T16:29:12+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-22T00:28:45+00:00</t>
+          <t>2026-10-22T16:29:12+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-22T00:28:45+00:00</t>
+          <t>2026-10-22T16:29:12+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-22T16:29:12+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-22T16:29:12+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-22T16:29:12+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-22T16:29:12+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-22T16:29:12+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-22T16:29:12+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-22T16:29:12+00:00</t>
+          <t>2026-10-22T19:50:09+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-22T16:29:12+00:00</t>
+          <t>2026-10-22T19:50:09+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-22T16:29:12+00:00</t>
+          <t>2026-10-22T19:50:09+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-22T16:29:12+00:00</t>
+          <t>2026-10-22T19:50:09+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-22T16:29:12+00:00</t>
+          <t>2026-10-22T19:50:09+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-22T16:29:12+00:00</t>
+          <t>2026-10-22T19:50:09+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-22T16:29:12+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-22T16:29:12+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-22T16:29:12+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-22T16:29:12+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-22T16:29:12+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-22T16:29:12+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-22T19:50:09+00:00</t>
+          <t>2026-10-23T00:26:34+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-22T19:50:09+00:00</t>
+          <t>2026-10-23T00:26:34+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-22T19:50:09+00:00</t>
+          <t>2026-10-23T00:26:34+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-22T19:50:09+00:00</t>
+          <t>2026-10-23T00:26:34+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-22T19:50:09+00:00</t>
+          <t>2026-10-23T00:26:34+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-22T19:50:09+00:00</t>
+          <t>2026-10-23T00:26:34+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,732 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-23T00:26:34+00:00</t>
+          <t>2026-10-23T16:18:34+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-23T00:26:34+00:00</t>
+          <t>2026-10-23T16:18:34+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-23T00:26:34+00:00</t>
+          <t>2026-10-23T16:18:34+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-23T00:26:34+00:00</t>
+          <t>2026-10-23T16:18:34+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-23T00:26:34+00:00</t>
+          <t>2026-10-23T16:18:34+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-23T00:26:34+00:00</t>
+          <t>2026-10-23T16:18:34+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,732 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:26:34+00:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-23T16:18:34+00:00</t>
+          <t>2026-10-23T19:51:45+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-23T16:18:34+00:00</t>
+          <t>2026-10-23T19:51:45+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-23T16:18:34+00:00</t>
+          <t>2026-10-23T19:51:45+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-23T16:18:34+00:00</t>
+          <t>2026-10-23T19:51:45+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-23T16:18:34+00:00</t>
+          <t>2026-10-23T19:51:45+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-23T16:18:34+00:00</t>
+          <t>2026-10-23T19:51:45+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:51:45+00:00</t>
+          <t>2026-10-24T00:20:51+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:51:45+00:00</t>
+          <t>2026-10-24T00:20:51+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-23T19:51:45+00:00</t>
+          <t>2026-10-24T00:20:51+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-23T19:51:45+00:00</t>
+          <t>2026-10-24T00:20:51+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:51:45+00:00</t>
+          <t>2026-10-24T00:20:51+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:51:45+00:00</t>
+          <t>2026-10-24T00:20:51+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:51+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:51+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:51+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:51+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:51+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:51+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:51+00:00</t>
+          <t>2026-10-24T15:15:58+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:51+00:00</t>
+          <t>2026-10-24T15:15:58+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:51+00:00</t>
+          <t>2026-10-24T15:15:58+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:51+00:00</t>
+          <t>2026-10-24T15:15:58+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:51+00:00</t>
+          <t>2026-10-24T15:15:58+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:51+00:00</t>
+          <t>2026-10-24T15:15:58+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:51+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:51+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:51+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:51+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:51+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:51+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-24T15:15:58+00:00</t>
+          <t>2026-10-24T18:39:17+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24T15:15:58+00:00</t>
+          <t>2026-10-24T18:39:17+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-24T15:15:58+00:00</t>
+          <t>2026-10-24T18:39:17+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-24T15:15:58+00:00</t>
+          <t>2026-10-24T18:39:17+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:15:58+00:00</t>
+          <t>2026-10-24T18:39:17+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:15:58+00:00</t>
+          <t>2026-10-24T18:39:17+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-24T18:39:17+00:00</t>
+          <t>2026-10-25T00:03:48+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24T18:39:17+00:00</t>
+          <t>2026-10-25T00:03:48+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-24T18:39:17+00:00</t>
+          <t>2026-10-25T00:03:48+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-24T18:39:17+00:00</t>
+          <t>2026-10-25T00:03:48+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-24T18:39:17+00:00</t>
+          <t>2026-10-25T00:03:48+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24T18:39:17+00:00</t>
+          <t>2026-10-25T00:03:48+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-25T00:03:48+00:00</t>
+          <t>2026-10-25T15:26:25+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T00:03:48+00:00</t>
+          <t>2026-10-25T15:26:25+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-25T00:03:48+00:00</t>
+          <t>2026-10-25T15:26:25+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T00:03:48+00:00</t>
+          <t>2026-10-25T15:26:25+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:03:48+00:00</t>
+          <t>2026-10-25T15:26:25+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:03:48+00:00</t>
+          <t>2026-10-25T15:26:25+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-25T15:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-25T15:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-25T15:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-25T15:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-25T15:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-25T15:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-25T15:26:25+00:00</t>
+          <t>2026-10-25T18:48:01+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-25T18:48:01+00:00</t>
+          <t>2026-10-25T23:54:35+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T18:48:01+00:00</t>
+          <t>2026-10-25T23:54:35+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-25T18:48:01+00:00</t>
+          <t>2026-10-25T23:54:35+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T18:48:01+00:00</t>
+          <t>2026-10-25T23:54:35+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:48:01+00:00</t>
+          <t>2026-10-25T23:54:35+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:48:01+00:00</t>
+          <t>2026-10-25T23:54:35+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-25T18:48:01+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-25T18:48:01+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-25T18:48:01+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-25T18:48:01+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-25T18:48:01+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-25T18:48:01+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-25T23:54:35+00:00</t>
+          <t>2026-10-26T18:06:44+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T23:54:35+00:00</t>
+          <t>2026-10-26T18:06:44+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-25T23:54:35+00:00</t>
+          <t>2026-10-26T18:06:44+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T23:54:35+00:00</t>
+          <t>2026-10-26T18:06:44+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-25T23:54:35+00:00</t>
+          <t>2026-10-26T18:06:44+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T23:54:35+00:00</t>
+          <t>2026-10-26T18:06:44+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-26T18:06:44+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-26T18:06:44+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-26T18:06:44+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-26T18:06:44+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-26T18:06:44+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-26T18:06:44+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-27T17:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-27T17:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-27T17:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-27T17:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-27T17:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-27T17:17:26+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-27T17:17:26+00:00</t>
+          <t>2026-10-27T20:30:36+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T17:17:26+00:00</t>
+          <t>2026-10-27T20:30:36+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-27T17:17:26+00:00</t>
+          <t>2026-10-27T20:30:36+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T17:17:26+00:00</t>
+          <t>2026-10-27T20:30:36+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-27T17:17:26+00:00</t>
+          <t>2026-10-27T20:30:36+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T17:17:26+00:00</t>
+          <t>2026-10-27T20:30:36+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,369 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-27T20:30:36+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-27T20:30:36+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-27T20:30:36+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-27T20:30:36+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-27T20:30:36+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-27T20:30:36+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T20:30:36+00:00</t>
+          <t>2026-10-28T01:01:27+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -971,7 +971,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#main-search</t>
+          <t>https://www.immo971.com/biens#main-search</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1092,7 +1092,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#nav-main</t>
+          <t>https://www.immo971.com/biens#nav-main</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1213,7 +1213,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens-a-vendre/#skip-content</t>
+          <t>https://www.immo971.com/biens#skip-content</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-28T01:01:27+00:00</t>
+          <t>2026-10-28T17:48:41+00:00</t>
         </is>
       </c>
       <c r="AB7" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:48:41+00:00</t>
+          <t>2026-10-28T20:51:55+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:48:41+00:00</t>
+          <t>2026-10-28T20:51:55+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-28T17:48:41+00:00</t>
+          <t>2026-10-28T20:51:55+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-28T17:48:41+00:00</t>
+          <t>2026-10-28T20:51:55+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:48:41+00:00</t>
+          <t>2026-10-28T20:51:55+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:48:41+00:00</t>
+          <t>2026-10-28T20:51:55+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,369 +963,6 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#main-search</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2026-10-28T17:48:41+00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-28T17:48:41+00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#nav-main</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2026-10-28T17:48:41+00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-28T17:48:41+00:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/biens#skip-content</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2026-10-28T17:48:41+00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-28T17:48:41+00:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/biens-a-vendre#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-28T20:51:55+00:00</t>
+          <t>2026-10-29T01:38:00+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-28T20:51:55+00:00</t>
+          <t>2026-10-29T01:38:00+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/biens-a-vendre#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-28T20:51:55+00:00</t>
+          <t>2026-10-29T01:38:00+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-28T20:51:55+00:00</t>
+          <t>2026-10-29T01:38:00+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/biens-a-vendre#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-28T20:51:55+00:00</t>
+          <t>2026-10-29T01:38:00+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-28T20:51:55+00:00</t>
+          <t>2026-10-29T01:38:00+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -963,6 +963,732 @@
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#main-search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#nav-main</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/biens#skip-content</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:38:00+00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-29T20:56:50+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-29T20:56:50+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-29T20:56:50+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-29T20:56:50+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-29T20:56:50+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-29T20:56:50+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>price_drop_pct_x</t>
+          <t>price_drop_pct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>status_x</t>
+          <t>status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -556,415 +556,17 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>first_seen</t>
+          <t>is_returned</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>last_seen</t>
+          <t>score</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>last_price</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>status_y</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct_y</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>price_drop_pct</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_returned</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
           <t>explications</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-10-29T20:56:50+00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-10-29T20:56:50+00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2026-10-29T20:56:50+00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-10-29T20:56:50+00:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BIENVENUE SURNOTRE SITE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>www.immo971.com</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-10-29T20:56:50+00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-10-29T20:56:50+00:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>198500</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,82 +491,480 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>price_drop_pct_x</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rent_potential</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>capex_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yield_net</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>division_possible</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>colocation_ready</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dist_amen_min</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>status_y</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>price_drop_pct_y</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>price_drop_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rent_potential</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>capex_ratio</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>yield_net</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>division_possible</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>colocation_ready</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>outdoor</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sanitation</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dist_amen_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_returned</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>explications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#main-search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-10-30T17:38:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-30T17:38:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#nav-main</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-30T17:38:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-30T17:38:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIENVENUE SURNOTRE SITE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.immo971.com/annonces/#skip-content</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>www.immo971.com</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-10-30T17:38:24+00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-30T17:38:24+00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>198500</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>✅ OK Localisation &amp; Urbanisme (+20.0); ✅ OK Localisation &amp; Urbanisme (+15.0); ✅ OK Localisation &amp; Urbanisme (+5.0); ✅ OK Caractéristiques du bien (+15.0); ✅ OK Caractéristiques du bien (+10.0); ✅ OK Travaux &amp; Potentiel (+25.0); ❌ Exclusion (Travaux &amp; Potentiel)</t>
         </is>
       </c>
     </row>

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#main-search</t>
+          <t>https://www.immo971.com/biens/#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:38:24+00:00</t>
+          <t>2026-10-30T20:31:56+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T17:38:24+00:00</t>
+          <t>2026-10-30T20:31:56+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#nav-main</t>
+          <t>https://www.immo971.com/biens/#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-30T17:38:24+00:00</t>
+          <t>2026-10-30T20:31:56+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T17:38:24+00:00</t>
+          <t>2026-10-30T20:31:56+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/annonces/#skip-content</t>
+          <t>https://www.immo971.com/biens/#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-30T17:38:24+00:00</t>
+          <t>2026-10-30T20:31:56+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T17:38:24+00:00</t>
+          <t>2026-10-30T20:31:56+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">

--- a/output/top10.xlsx
+++ b/output/top10.xlsx
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#main-search</t>
+          <t>https://www.immo971.com/annonces#main-search</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -687,12 +687,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-10-30T20:31:56+00:00</t>
+          <t>2026-10-31T01:27:13+00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T20:31:56+00:00</t>
+          <t>2026-10-31T01:27:13+00:00</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -729,7 +729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#nav-main</t>
+          <t>https://www.immo971.com/annonces#nav-main</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -808,12 +808,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-10-30T20:31:56+00:00</t>
+          <t>2026-10-31T01:27:13+00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T20:31:56+00:00</t>
+          <t>2026-10-31T01:27:13+00:00</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -850,7 +850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.immo971.com/biens/#skip-content</t>
+          <t>https://www.immo971.com/annonces#skip-content</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -929,12 +929,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-10-30T20:31:56+00:00</t>
+          <t>2026-10-31T01:27:13+00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T20:31:56+00:00</t>
+          <t>2026-10-31T01:27:13+00:00</t>
         </is>
       </c>
       <c r="AB4" t="n">
